--- a/data/attendance/ANNEX_فردي_2_ثانوي.xlsx
+++ b/data/attendance/ANNEX_فردي_2_ثانوي.xlsx
@@ -20,6 +20,13 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
+          <t>student_id:399a5570-e979-4d5b-a709-c544a14bbefe</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0">
+      <text>
+        <r>
           <t>student_id:6eb5e29c-8e60-4130-af22-5e34fdd483a4</t>
         </r>
       </text>
@@ -29,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
   <si>
     <t>فردي 2 ثانوي  |  ANNEX  |  2AS  |  فردي خلود</t>
   </si>
@@ -43,6 +50,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -52,9 +62,15 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
+    <t>03/10/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
+    <t>بوعناقة سيرين</t>
+  </si>
+  <si>
     <t>خنيو لجين</t>
   </si>
   <si>
@@ -85,7 +101,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -136,7 +155,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -173,6 +192,11 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F5FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -201,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -225,6 +249,9 @@
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -567,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -593,7 +620,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -603,10 +630,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -648,89 +678,133 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
+        <v>379</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+      <c r="N5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>453</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0</v>
-      </c>
-      <c r="F5" s="8">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8">
+      <c r="B6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9">
+        <v>0</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0</v>
+      </c>
+      <c r="N6" s="9">
         <v>0</v>
       </c>
     </row>
@@ -750,85 +824,90 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>9</v>
+      <c r="A1" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
